--- a/instrumentos/sesion-04/Sesion 4.xlsx
+++ b/instrumentos/sesion-04/Sesion 4.xlsx
@@ -2458,7 +2458,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Aplicación multiplataforma de búsqueda semántica conversacional (PWA + RAG) — v1.0.0-frozen-2026-10-26</t>
+          <t>Aplicación multiplataforma de búsqueda semántica conversacional (PWA + RAG) — v1.0.0-frozen-2026-10-18</t>
         </is>
       </c>
       <c r="C10" s="58" t="n"/>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="B11" s="60" t="n">
-        <v>46322.375</v>
+        <v>46314.375</v>
       </c>
       <c r="C11" s="58" t="n"/>
       <c r="D11" s="58" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>HTTPS en chat.tudiariohuanuco.pe el 26/10/2026.</t>
+          <t>HTTPS en chat.tudiariohuanuco.pe el 18/10/2026.</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="D13" s="30" t="inlineStr">
         <is>
-          <t>Tag v1.0.0-frozen-2026-10-26. Sin deploys hasta el postest.</t>
+          <t>Tag v1.0.0-frozen-2026-10-18. Sin deploys hasta el postest.</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Datos de prueba eliminados el 26/10/2026.</t>
+          <t>Datos de prueba eliminados el 18/10/2026.</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Acta T0 del 27/10/2026 (hoja 09).</t>
+          <t>Acta T0 del 19/10/2026 (hoja 09).</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr"/>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="B7" s="40" t="inlineStr">
         <is>
-          <t>v1.0.0-frozen-2026-10-26</t>
+          <t>v1.0.0-frozen-2026-10-18</t>
         </is>
       </c>
       <c r="C7" s="73" t="n"/>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="B11" s="74" t="n">
-        <v>46321.77083333334</v>
+        <v>46313.77083333334</v>
       </c>
       <c r="C11" s="73" t="n"/>
       <c r="D11" s="73" t="n"/>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>v1.0.0-frozen-2026-10-26</t>
+          <t>v1.0.0-frozen-2026-10-18</t>
         </is>
       </c>
       <c r="C18" s="34" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="B19" s="36" t="inlineStr">
         <is>
-          <t>v1.0.0-frozen-2026-10-26</t>
+          <t>v1.0.0-frozen-2026-10-18</t>
         </is>
       </c>
       <c r="C19" s="37" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>v1.0.0-frozen-2026-10-26</t>
+          <t>v1.0.0-frozen-2026-10-18</t>
         </is>
       </c>
       <c r="C20" s="36" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="B21" s="36" t="inlineStr">
         <is>
-          <t>v1.0.0-frozen-2026-10-26</t>
+          <t>v1.0.0-frozen-2026-10-18</t>
         </is>
       </c>
       <c r="C21" s="36" t="inlineStr">
@@ -9150,7 +9150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="71" min="1" max="1"/>
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="F12" s="75" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="F13" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         </is>
       </c>
       <c r="F14" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="F15" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G15" s="23" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="F16" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="F17" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="F18" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="F19" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="F20" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         </is>
       </c>
       <c r="F21" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         </is>
       </c>
       <c r="F22" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="F23" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         </is>
       </c>
       <c r="F24" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="F25" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="F26" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="F27" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="F28" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         </is>
       </c>
       <c r="F29" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="F30" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="F31" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="F32" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="F33" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="F34" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         </is>
       </c>
       <c r="F35" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         </is>
       </c>
       <c r="F36" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="F37" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G37" s="23" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         </is>
       </c>
       <c r="F38" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="F39" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G39" s="23" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="F40" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="F41" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G41" s="23" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         </is>
       </c>
       <c r="F42" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="F43" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G43" s="23" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="F44" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G44" s="23" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="F45" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="F46" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         </is>
       </c>
       <c r="F47" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="F48" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G48" s="23" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="F49" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="F50" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="F51" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="F52" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G52" s="23" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         </is>
       </c>
       <c r="F53" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F54" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="F55" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="F56" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G56" s="23" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="F57" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G57" s="23" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         </is>
       </c>
       <c r="F58" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="F59" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G59" s="23" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="F60" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="F61" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G61" s="23" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         </is>
       </c>
       <c r="F62" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G62" s="23" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="F63" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         </is>
       </c>
       <c r="F64" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G64" s="23" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         </is>
       </c>
       <c r="F65" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G65" s="23" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="F66" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G66" s="23" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         </is>
       </c>
       <c r="F67" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G67" s="23" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="F68" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G68" s="23" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="F69" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G69" s="23" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="F70" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G70" s="23" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         </is>
       </c>
       <c r="F71" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G71" s="23" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="F72" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G72" s="23" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="F73" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G73" s="23" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="F74" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G74" s="23" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         </is>
       </c>
       <c r="F75" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G75" s="23" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="F76" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G76" s="23" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         </is>
       </c>
       <c r="F77" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G77" s="23" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         </is>
       </c>
       <c r="F78" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G78" s="23" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         </is>
       </c>
       <c r="F79" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G79" s="23" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="F80" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G80" s="23" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         </is>
       </c>
       <c r="F81" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G81" s="23" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         </is>
       </c>
       <c r="F82" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G82" s="23" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         </is>
       </c>
       <c r="F83" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G83" s="23" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         </is>
       </c>
       <c r="F84" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G84" s="23" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="F85" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G85" s="23" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         </is>
       </c>
       <c r="F86" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G86" s="23" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="F87" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G87" s="23" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="F88" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G88" s="23" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         </is>
       </c>
       <c r="F89" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G89" s="23" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="F90" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G90" s="23" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="F91" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G91" s="23" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="F92" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G92" s="23" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         </is>
       </c>
       <c r="F93" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G93" s="23" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         </is>
       </c>
       <c r="F94" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G94" s="23" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         </is>
       </c>
       <c r="F95" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G95" s="23" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="F96" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G96" s="23" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="F97" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G97" s="23" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="F98" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G98" s="23" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         </is>
       </c>
       <c r="F99" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G99" s="23" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="F100" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G100" s="23" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         </is>
       </c>
       <c r="F101" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G101" s="23" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="F102" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G102" s="23" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="F103" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G103" s="23" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="F104" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G104" s="23" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="F105" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G105" s="23" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="F106" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G106" s="23" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         </is>
       </c>
       <c r="F107" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G107" s="23" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         </is>
       </c>
       <c r="F108" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G108" s="23" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         </is>
       </c>
       <c r="F109" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G109" s="23" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="F110" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G110" s="23" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="F111" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G111" s="23" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="F112" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G112" s="23" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         </is>
       </c>
       <c r="F113" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G113" s="23" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         </is>
       </c>
       <c r="F114" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G114" s="23" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="F115" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G115" s="23" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         </is>
       </c>
       <c r="F116" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G116" s="23" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         </is>
       </c>
       <c r="F117" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G117" s="23" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="F118" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G118" s="23" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         </is>
       </c>
       <c r="F119" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="G119" s="23" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         </is>
       </c>
       <c r="H12" s="75" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="71">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="H13" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="71">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="H14" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="71">
@@ -14887,7 +14887,7 @@
         </is>
       </c>
       <c r="H15" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="71">
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="H16" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="71">
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="H17" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="71">
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="H18" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="71">
@@ -15047,7 +15047,7 @@
         </is>
       </c>
       <c r="H19" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="71">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="H20" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="71">
@@ -15127,7 +15127,7 @@
         </is>
       </c>
       <c r="H21" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="71">
@@ -15167,7 +15167,7 @@
         </is>
       </c>
       <c r="H22" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="71">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="H23" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="71">
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="I12" s="75" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="71">
@@ -16613,7 +16613,7 @@
         </is>
       </c>
       <c r="I13" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="71">
@@ -16658,7 +16658,7 @@
         </is>
       </c>
       <c r="I14" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="71">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="I15" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="71">
@@ -16748,7 +16748,7 @@
         </is>
       </c>
       <c r="I16" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="71">
@@ -16793,7 +16793,7 @@
         </is>
       </c>
       <c r="I17" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="71">
@@ -16838,7 +16838,7 @@
         </is>
       </c>
       <c r="I18" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="71">
@@ -16883,7 +16883,7 @@
         </is>
       </c>
       <c r="I19" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="71">
@@ -16928,7 +16928,7 @@
         </is>
       </c>
       <c r="I20" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="71">
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="I21" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="71">
@@ -18368,13 +18368,13 @@
         </is>
       </c>
       <c r="C14" s="47" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D14" s="48" t="n">
-        <v>46320.41666666666</v>
+        <v>46312.41666666666</v>
       </c>
       <c r="E14" s="48" t="n">
-        <v>46320.43402777778</v>
+        <v>46312.43402777778</v>
       </c>
       <c r="F14" s="24">
         <f>IF(OR(D14="",E14=""),"",ROUND((E14-D14)*1440,0))</f>
@@ -18410,13 +18410,13 @@
         </is>
       </c>
       <c r="C15" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D15" s="53" t="n">
-        <v>46320.66875</v>
+        <v>46312.66875</v>
       </c>
       <c r="E15" s="53" t="n">
-        <v>46320.68611111111</v>
+        <v>46312.68611111111</v>
       </c>
       <c r="F15" s="21">
         <f>IF(OR(D15="",E15=""),"",ROUND((E15-D15)*1440,0))</f>
@@ -18452,13 +18452,13 @@
         </is>
       </c>
       <c r="C16" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D16" s="53" t="n">
-        <v>46320.42083333333</v>
+        <v>46312.42083333333</v>
       </c>
       <c r="E16" s="53" t="n">
-        <v>46320.43819444445</v>
+        <v>46312.43819444445</v>
       </c>
       <c r="F16" s="21">
         <f>IF(OR(D16="",E16=""),"",ROUND((E16-D16)*1440,0))</f>
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="C17" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D17" s="53" t="n">
-        <v>46320.67291666667</v>
+        <v>46312.67291666667</v>
       </c>
       <c r="E17" s="53" t="n">
-        <v>46320.69027777778</v>
+        <v>46312.69027777778</v>
       </c>
       <c r="F17" s="21">
         <f>IF(OR(D17="",E17=""),"",ROUND((E17-D17)*1440,0))</f>
@@ -18536,13 +18536,13 @@
         </is>
       </c>
       <c r="C18" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D18" s="53" t="n">
-        <v>46320.425</v>
+        <v>46312.425</v>
       </c>
       <c r="E18" s="53" t="n">
-        <v>46320.44236111111</v>
+        <v>46312.44236111111</v>
       </c>
       <c r="F18" s="21">
         <f>IF(OR(D18="",E18=""),"",ROUND((E18-D18)*1440,0))</f>
@@ -18578,13 +18578,13 @@
         </is>
       </c>
       <c r="C19" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D19" s="53" t="n">
-        <v>46320.67708333334</v>
+        <v>46312.67708333334</v>
       </c>
       <c r="E19" s="53" t="n">
-        <v>46320.69444444445</v>
+        <v>46312.69444444445</v>
       </c>
       <c r="F19" s="21">
         <f>IF(OR(D19="",E19=""),"",ROUND((E19-D19)*1440,0))</f>
@@ -18620,13 +18620,13 @@
         </is>
       </c>
       <c r="C20" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D20" s="53" t="n">
-        <v>46320.42916666667</v>
+        <v>46312.42916666667</v>
       </c>
       <c r="E20" s="53" t="n">
-        <v>46320.44652777778</v>
+        <v>46312.44652777778</v>
       </c>
       <c r="F20" s="21">
         <f>IF(OR(D20="",E20=""),"",ROUND((E20-D20)*1440,0))</f>
@@ -18662,13 +18662,13 @@
         </is>
       </c>
       <c r="C21" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D21" s="53" t="n">
-        <v>46320.68125</v>
+        <v>46312.68125</v>
       </c>
       <c r="E21" s="53" t="n">
-        <v>46320.69861111111</v>
+        <v>46312.69861111111</v>
       </c>
       <c r="F21" s="21">
         <f>IF(OR(D21="",E21=""),"",ROUND((E21-D21)*1440,0))</f>
@@ -18704,13 +18704,13 @@
         </is>
       </c>
       <c r="C22" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D22" s="53" t="n">
-        <v>46320.43333333333</v>
+        <v>46312.43333333333</v>
       </c>
       <c r="E22" s="53" t="n">
-        <v>46320.45069444444</v>
+        <v>46312.45069444444</v>
       </c>
       <c r="F22" s="21">
         <f>IF(OR(D22="",E22=""),"",ROUND((E22-D22)*1440,0))</f>
@@ -18746,13 +18746,13 @@
         </is>
       </c>
       <c r="C23" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D23" s="53" t="n">
-        <v>46320.68541666667</v>
+        <v>46312.68541666667</v>
       </c>
       <c r="E23" s="53" t="n">
-        <v>46320.70277777778</v>
+        <v>46312.70277777778</v>
       </c>
       <c r="F23" s="21">
         <f>IF(OR(D23="",E23=""),"",ROUND((E23-D23)*1440,0))</f>
@@ -18788,13 +18788,13 @@
         </is>
       </c>
       <c r="C24" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D24" s="53" t="n">
-        <v>46320.4375</v>
+        <v>46312.4375</v>
       </c>
       <c r="E24" s="53" t="n">
-        <v>46320.45486111111</v>
+        <v>46312.45486111111</v>
       </c>
       <c r="F24" s="21">
         <f>IF(OR(D24="",E24=""),"",ROUND((E24-D24)*1440,0))</f>
@@ -18830,13 +18830,13 @@
         </is>
       </c>
       <c r="C25" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D25" s="53" t="n">
-        <v>46320.68958333333</v>
+        <v>46312.68958333333</v>
       </c>
       <c r="E25" s="53" t="n">
-        <v>46320.70694444444</v>
+        <v>46312.70694444444</v>
       </c>
       <c r="F25" s="21">
         <f>IF(OR(D25="",E25=""),"",ROUND((E25-D25)*1440,0))</f>
@@ -18872,13 +18872,13 @@
         </is>
       </c>
       <c r="C26" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D26" s="53" t="n">
-        <v>46320.44166666667</v>
+        <v>46312.44166666667</v>
       </c>
       <c r="E26" s="53" t="n">
-        <v>46320.45902777778</v>
+        <v>46312.45902777778</v>
       </c>
       <c r="F26" s="21">
         <f>IF(OR(D26="",E26=""),"",ROUND((E26-D26)*1440,0))</f>
@@ -18914,13 +18914,13 @@
         </is>
       </c>
       <c r="C27" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D27" s="53" t="n">
-        <v>46320.69375</v>
+        <v>46312.69375</v>
       </c>
       <c r="E27" s="53" t="n">
-        <v>46320.71111111111</v>
+        <v>46312.71111111111</v>
       </c>
       <c r="F27" s="21">
         <f>IF(OR(D27="",E27=""),"",ROUND((E27-D27)*1440,0))</f>
@@ -18956,13 +18956,13 @@
         </is>
       </c>
       <c r="C28" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D28" s="53" t="n">
-        <v>46320.44583333333</v>
+        <v>46312.44583333333</v>
       </c>
       <c r="E28" s="53" t="n">
-        <v>46320.46319444444</v>
+        <v>46312.46319444444</v>
       </c>
       <c r="F28" s="21">
         <f>IF(OR(D28="",E28=""),"",ROUND((E28-D28)*1440,0))</f>
@@ -18998,13 +18998,13 @@
         </is>
       </c>
       <c r="C29" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D29" s="53" t="n">
-        <v>46320.69791666666</v>
+        <v>46312.69791666666</v>
       </c>
       <c r="E29" s="53" t="n">
-        <v>46320.71527777778</v>
+        <v>46312.71527777778</v>
       </c>
       <c r="F29" s="21">
         <f>IF(OR(D29="",E29=""),"",ROUND((E29-D29)*1440,0))</f>
@@ -19040,13 +19040,13 @@
         </is>
       </c>
       <c r="C30" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D30" s="53" t="n">
-        <v>46320.45</v>
+        <v>46312.45</v>
       </c>
       <c r="E30" s="53" t="n">
-        <v>46320.46736111111</v>
+        <v>46312.46736111111</v>
       </c>
       <c r="F30" s="21">
         <f>IF(OR(D30="",E30=""),"",ROUND((E30-D30)*1440,0))</f>
@@ -19082,13 +19082,13 @@
         </is>
       </c>
       <c r="C31" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D31" s="53" t="n">
-        <v>46320.66736111111</v>
+        <v>46312.66736111111</v>
       </c>
       <c r="E31" s="53" t="n">
-        <v>46320.68472222222</v>
+        <v>46312.68472222222</v>
       </c>
       <c r="F31" s="21">
         <f>IF(OR(D31="",E31=""),"",ROUND((E31-D31)*1440,0))</f>
@@ -19124,13 +19124,13 @@
         </is>
       </c>
       <c r="C32" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D32" s="53" t="n">
-        <v>46320.41944444444</v>
+        <v>46312.41944444444</v>
       </c>
       <c r="E32" s="53" t="n">
-        <v>46320.43680555555</v>
+        <v>46312.43680555555</v>
       </c>
       <c r="F32" s="21">
         <f>IF(OR(D32="",E32=""),"",ROUND((E32-D32)*1440,0))</f>
@@ -19166,13 +19166,13 @@
         </is>
       </c>
       <c r="C33" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D33" s="53" t="n">
-        <v>46320.67152777778</v>
+        <v>46312.67152777778</v>
       </c>
       <c r="E33" s="53" t="n">
-        <v>46320.68888888889</v>
+        <v>46312.68888888889</v>
       </c>
       <c r="F33" s="21">
         <f>IF(OR(D33="",E33=""),"",ROUND((E33-D33)*1440,0))</f>
@@ -19208,13 +19208,13 @@
         </is>
       </c>
       <c r="C34" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D34" s="53" t="n">
-        <v>46320.42361111111</v>
+        <v>46312.42361111111</v>
       </c>
       <c r="E34" s="53" t="n">
-        <v>46320.44097222222</v>
+        <v>46312.44097222222</v>
       </c>
       <c r="F34" s="21">
         <f>IF(OR(D34="",E34=""),"",ROUND((E34-D34)*1440,0))</f>
@@ -19250,13 +19250,13 @@
         </is>
       </c>
       <c r="C35" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D35" s="53" t="n">
-        <v>46320.67569444444</v>
+        <v>46312.67569444444</v>
       </c>
       <c r="E35" s="53" t="n">
-        <v>46320.69305555556</v>
+        <v>46312.69305555556</v>
       </c>
       <c r="F35" s="21">
         <f>IF(OR(D35="",E35=""),"",ROUND((E35-D35)*1440,0))</f>
@@ -19292,13 +19292,13 @@
         </is>
       </c>
       <c r="C36" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D36" s="53" t="n">
-        <v>46320.42777777778</v>
+        <v>46312.42777777778</v>
       </c>
       <c r="E36" s="53" t="n">
-        <v>46320.44513888889</v>
+        <v>46312.44513888889</v>
       </c>
       <c r="F36" s="21">
         <f>IF(OR(D36="",E36=""),"",ROUND((E36-D36)*1440,0))</f>
@@ -19334,13 +19334,13 @@
         </is>
       </c>
       <c r="C37" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D37" s="53" t="n">
-        <v>46320.67986111111</v>
+        <v>46312.67986111111</v>
       </c>
       <c r="E37" s="53" t="n">
-        <v>46320.69722222222</v>
+        <v>46312.69722222222</v>
       </c>
       <c r="F37" s="21">
         <f>IF(OR(D37="",E37=""),"",ROUND((E37-D37)*1440,0))</f>
@@ -19376,13 +19376,13 @@
         </is>
       </c>
       <c r="C38" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D38" s="53" t="n">
-        <v>46320.43194444444</v>
+        <v>46312.43194444444</v>
       </c>
       <c r="E38" s="53" t="n">
-        <v>46320.44930555556</v>
+        <v>46312.44930555556</v>
       </c>
       <c r="F38" s="21">
         <f>IF(OR(D38="",E38=""),"",ROUND((E38-D38)*1440,0))</f>
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="C39" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D39" s="53" t="n">
-        <v>46320.68402777778</v>
+        <v>46312.68402777778</v>
       </c>
       <c r="E39" s="53" t="n">
-        <v>46320.70138888889</v>
+        <v>46312.70138888889</v>
       </c>
       <c r="F39" s="21">
         <f>IF(OR(D39="",E39=""),"",ROUND((E39-D39)*1440,0))</f>
@@ -19460,13 +19460,13 @@
         </is>
       </c>
       <c r="C40" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D40" s="53" t="n">
-        <v>46320.43611111111</v>
+        <v>46312.43611111111</v>
       </c>
       <c r="E40" s="53" t="n">
-        <v>46320.45347222222</v>
+        <v>46312.45347222222</v>
       </c>
       <c r="F40" s="21">
         <f>IF(OR(D40="",E40=""),"",ROUND((E40-D40)*1440,0))</f>
@@ -19502,13 +19502,13 @@
         </is>
       </c>
       <c r="C41" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D41" s="53" t="n">
-        <v>46320.68819444445</v>
+        <v>46312.68819444445</v>
       </c>
       <c r="E41" s="53" t="n">
-        <v>46320.70555555556</v>
+        <v>46312.70555555556</v>
       </c>
       <c r="F41" s="21">
         <f>IF(OR(D41="",E41=""),"",ROUND((E41-D41)*1440,0))</f>
@@ -19544,13 +19544,13 @@
         </is>
       </c>
       <c r="C42" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D42" s="53" t="n">
-        <v>46320.44027777778</v>
+        <v>46312.44027777778</v>
       </c>
       <c r="E42" s="53" t="n">
-        <v>46320.45763888889</v>
+        <v>46312.45763888889</v>
       </c>
       <c r="F42" s="21">
         <f>IF(OR(D42="",E42=""),"",ROUND((E42-D42)*1440,0))</f>
@@ -19586,13 +19586,13 @@
         </is>
       </c>
       <c r="C43" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D43" s="53" t="n">
-        <v>46320.69236111111</v>
+        <v>46312.69236111111</v>
       </c>
       <c r="E43" s="53" t="n">
-        <v>46320.70972222222</v>
+        <v>46312.70972222222</v>
       </c>
       <c r="F43" s="21">
         <f>IF(OR(D43="",E43=""),"",ROUND((E43-D43)*1440,0))</f>
@@ -19628,13 +19628,13 @@
         </is>
       </c>
       <c r="C44" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D44" s="53" t="n">
-        <v>46320.45</v>
+        <v>46312.45</v>
       </c>
       <c r="E44" s="53" t="n">
-        <v>46320.46736111111</v>
+        <v>46312.46736111111</v>
       </c>
       <c r="F44" s="21">
         <f>IF(OR(D44="",E44=""),"",ROUND((E44-D44)*1440,0))</f>
@@ -19670,13 +19670,13 @@
         </is>
       </c>
       <c r="C45" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D45" s="53" t="n">
-        <v>46320.5375</v>
+        <v>46312.5375</v>
       </c>
       <c r="E45" s="53" t="n">
-        <v>46320.55486111111</v>
+        <v>46312.55486111111</v>
       </c>
       <c r="F45" s="21">
         <f>IF(OR(D45="",E123=""),"",ROUND((E123-D45)*1440,0))</f>
@@ -19712,13 +19712,13 @@
         </is>
       </c>
       <c r="C46" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D46" s="53" t="n">
-        <v>46320.58125</v>
+        <v>46312.58125</v>
       </c>
       <c r="E46" s="53" t="n">
-        <v>46320.59861111111</v>
+        <v>46312.59861111111</v>
       </c>
       <c r="F46" s="21">
         <f>IF(OR(D46="",E124=""),"",ROUND((E124-D46)*1440,0))</f>
@@ -19754,13 +19754,13 @@
         </is>
       </c>
       <c r="C47" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D47" s="53" t="n">
-        <v>46320.58333333334</v>
+        <v>46312.58333333334</v>
       </c>
       <c r="E47" s="53" t="n">
-        <v>46320.60069444445</v>
+        <v>46312.60069444445</v>
       </c>
       <c r="F47" s="21">
         <f>IF(OR(D47="",E47=""),"",ROUND((E47-D47)*1440,0))</f>
@@ -19796,13 +19796,13 @@
         </is>
       </c>
       <c r="C48" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D48" s="53" t="n">
-        <v>46320.62708333333</v>
+        <v>46312.62708333333</v>
       </c>
       <c r="E48" s="53" t="n">
-        <v>46320.64444444444</v>
+        <v>46312.64444444444</v>
       </c>
       <c r="F48" s="21">
         <f>IF(OR(D48="",E48=""),"",ROUND((E48-D48)*1440,0))</f>
@@ -19838,13 +19838,13 @@
         </is>
       </c>
       <c r="C49" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D49" s="53" t="n">
-        <v>46320.42083333333</v>
+        <v>46312.42083333333</v>
       </c>
       <c r="E49" s="53" t="n">
-        <v>46320.43819444445</v>
+        <v>46312.43819444445</v>
       </c>
       <c r="F49" s="21">
         <f>IF(OR(D49="",E49=""),"",ROUND((E49-D49)*1440,0))</f>
@@ -19880,13 +19880,13 @@
         </is>
       </c>
       <c r="C50" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D50" s="53" t="n">
-        <v>46320.46458333333</v>
+        <v>46312.46458333333</v>
       </c>
       <c r="E50" s="53" t="n">
-        <v>46320.48194444444</v>
+        <v>46312.48194444444</v>
       </c>
       <c r="F50" s="21">
         <f>IF(OR(D50="",E50=""),"",ROUND((E50-D50)*1440,0))</f>
@@ -19922,13 +19922,13 @@
         </is>
       </c>
       <c r="C51" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D51" s="53" t="n">
-        <v>46320.55208333334</v>
+        <v>46312.55208333334</v>
       </c>
       <c r="E51" s="53" t="n">
-        <v>46320.56944444445</v>
+        <v>46312.56944444445</v>
       </c>
       <c r="F51" s="21">
         <f>IF(OR(D51="",E51=""),"",ROUND((E51-D51)*1440,0))</f>
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="C52" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D52" s="53" t="n">
-        <v>46320.63958333333</v>
+        <v>46312.63958333333</v>
       </c>
       <c r="E52" s="53" t="n">
-        <v>46320.65694444445</v>
+        <v>46312.65694444445</v>
       </c>
       <c r="F52" s="21">
         <f>IF(OR(D52="",E52=""),"",ROUND((E52-D52)*1440,0))</f>
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="C53" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D53" s="53" t="n">
-        <v>46320.43333333333</v>
+        <v>46312.43333333333</v>
       </c>
       <c r="E53" s="53" t="n">
-        <v>46320.45069444444</v>
+        <v>46312.45069444444</v>
       </c>
       <c r="F53" s="21">
         <f>IF(OR(D53="",E53=""),"",ROUND((E53-D53)*1440,0))</f>
@@ -20048,13 +20048,13 @@
         </is>
       </c>
       <c r="C54" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D54" s="53" t="n">
-        <v>46320.47708333333</v>
+        <v>46312.47708333333</v>
       </c>
       <c r="E54" s="53" t="n">
-        <v>46320.49444444444</v>
+        <v>46312.49444444444</v>
       </c>
       <c r="F54" s="21">
         <f>IF(OR(D54="",E54=""),"",ROUND((E54-D54)*1440,0))</f>
@@ -20090,13 +20090,13 @@
         </is>
       </c>
       <c r="C55" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D55" s="53" t="n">
-        <v>46320.52083333334</v>
+        <v>46312.52083333334</v>
       </c>
       <c r="E55" s="53" t="n">
-        <v>46320.53819444445</v>
+        <v>46312.53819444445</v>
       </c>
       <c r="F55" s="21">
         <f>IF(OR(D55="",E55=""),"",ROUND((E55-D55)*1440,0))</f>
@@ -20132,13 +20132,13 @@
         </is>
       </c>
       <c r="C56" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D56" s="53" t="n">
-        <v>46320.56458333333</v>
+        <v>46312.56458333333</v>
       </c>
       <c r="E56" s="53" t="n">
-        <v>46320.58194444444</v>
+        <v>46312.58194444444</v>
       </c>
       <c r="F56" s="21">
         <f>IF(OR(D56="",E56=""),"",ROUND((E56-D56)*1440,0))</f>
@@ -20174,13 +20174,13 @@
         </is>
       </c>
       <c r="C57" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D57" s="53" t="n">
-        <v>46320.60833333333</v>
+        <v>46312.60833333333</v>
       </c>
       <c r="E57" s="53" t="n">
-        <v>46320.62569444445</v>
+        <v>46312.62569444445</v>
       </c>
       <c r="F57" s="21">
         <f>IF(OR(D57="",E57=""),"",ROUND((E57-D57)*1440,0))</f>
@@ -20216,13 +20216,13 @@
         </is>
       </c>
       <c r="C58" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D58" s="53" t="n">
-        <v>46320.65208333333</v>
+        <v>46312.65208333333</v>
       </c>
       <c r="E58" s="53" t="n">
-        <v>46320.66944444444</v>
+        <v>46312.66944444444</v>
       </c>
       <c r="F58" s="21">
         <f>IF(OR(D58="",E58=""),"",ROUND((E58-D58)*1440,0))</f>
@@ -20258,13 +20258,13 @@
         </is>
       </c>
       <c r="C59" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D59" s="53" t="n">
-        <v>46320.44583333333</v>
+        <v>46312.44583333333</v>
       </c>
       <c r="E59" s="53" t="n">
-        <v>46320.46319444444</v>
+        <v>46312.46319444444</v>
       </c>
       <c r="F59" s="21">
         <f>IF(OR(D59="",E59=""),"",ROUND((E59-D59)*1440,0))</f>
@@ -20300,13 +20300,13 @@
         </is>
       </c>
       <c r="C60" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D60" s="53" t="n">
-        <v>46320.53333333333</v>
+        <v>46312.53333333333</v>
       </c>
       <c r="E60" s="53" t="n">
-        <v>46320.55069444444</v>
+        <v>46312.55069444444</v>
       </c>
       <c r="F60" s="21">
         <f>IF(OR(D60="",E60=""),"",ROUND((E60-D60)*1440,0))</f>
@@ -20342,13 +20342,13 @@
         </is>
       </c>
       <c r="C61" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D61" s="53" t="n">
-        <v>46320.57708333333</v>
+        <v>46312.57708333333</v>
       </c>
       <c r="E61" s="53" t="n">
-        <v>46320.59444444445</v>
+        <v>46312.59444444445</v>
       </c>
       <c r="F61" s="21">
         <f>IF(OR(D61="",E61=""),"",ROUND((E61-D61)*1440,0))</f>
@@ -20384,13 +20384,13 @@
         </is>
       </c>
       <c r="C62" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D62" s="53" t="n">
-        <v>46320.62083333333</v>
+        <v>46312.62083333333</v>
       </c>
       <c r="E62" s="53" t="n">
-        <v>46320.63819444444</v>
+        <v>46312.63819444444</v>
       </c>
       <c r="F62" s="21">
         <f>IF(OR(D62="",E62=""),"",ROUND((E62-D62)*1440,0))</f>
@@ -20426,13 +20426,13 @@
         </is>
       </c>
       <c r="C63" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D63" s="53" t="n">
-        <v>46320.41666666666</v>
+        <v>46312.41666666666</v>
       </c>
       <c r="E63" s="53" t="n">
-        <v>46320.43402777778</v>
+        <v>46312.43402777778</v>
       </c>
       <c r="F63" s="21">
         <f>IF(OR(D63="",E63=""),"",ROUND((E63-D63)*1440,0))</f>
@@ -20468,13 +20468,13 @@
         </is>
       </c>
       <c r="C64" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D64" s="53" t="n">
-        <v>46320.46041666667</v>
+        <v>46312.46041666667</v>
       </c>
       <c r="E64" s="53" t="n">
-        <v>46320.47777777778</v>
+        <v>46312.47777777778</v>
       </c>
       <c r="F64" s="21">
         <f>IF(OR(D64="",E64=""),"",ROUND((E64-D64)*1440,0))</f>
@@ -20510,13 +20510,13 @@
         </is>
       </c>
       <c r="C65" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D65" s="53" t="n">
-        <v>46320.50416666667</v>
+        <v>46312.50416666667</v>
       </c>
       <c r="E65" s="53" t="n">
-        <v>46320.52152777778</v>
+        <v>46312.52152777778</v>
       </c>
       <c r="F65" s="21">
         <f>IF(OR(D65="",E65=""),"",ROUND((E65-D65)*1440,0))</f>
@@ -20552,13 +20552,13 @@
         </is>
       </c>
       <c r="C66" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D66" s="53" t="n">
-        <v>46320.54791666667</v>
+        <v>46312.54791666667</v>
       </c>
       <c r="E66" s="53" t="n">
-        <v>46320.56527777778</v>
+        <v>46312.56527777778</v>
       </c>
       <c r="F66" s="21">
         <f>IF(OR(D66="",E66=""),"",ROUND((E66-D66)*1440,0))</f>
@@ -20594,13 +20594,13 @@
         </is>
       </c>
       <c r="C67" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D67" s="53" t="n">
-        <v>46320.59166666667</v>
+        <v>46312.59166666667</v>
       </c>
       <c r="E67" s="53" t="n">
-        <v>46320.60902777778</v>
+        <v>46312.60902777778</v>
       </c>
       <c r="F67" s="21">
         <f>IF(OR(D67="",E67=""),"",ROUND((E67-D67)*1440,0))</f>
@@ -20636,13 +20636,13 @@
         </is>
       </c>
       <c r="C68" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D68" s="53" t="n">
-        <v>46320.63541666666</v>
+        <v>46312.63541666666</v>
       </c>
       <c r="E68" s="53" t="n">
-        <v>46320.65277777778</v>
+        <v>46312.65277777778</v>
       </c>
       <c r="F68" s="21">
         <f>IF(OR(D68="",E68=""),"",ROUND((E68-D68)*1440,0))</f>
@@ -20678,13 +20678,13 @@
         </is>
       </c>
       <c r="C69" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D69" s="53" t="n">
-        <v>46320.42916666667</v>
+        <v>46312.42916666667</v>
       </c>
       <c r="E69" s="53" t="n">
-        <v>46320.44652777778</v>
+        <v>46312.44652777778</v>
       </c>
       <c r="F69" s="21">
         <f>IF(OR(D69="",E69=""),"",ROUND((E69-D69)*1440,0))</f>
@@ -20720,13 +20720,13 @@
         </is>
       </c>
       <c r="C70" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D70" s="53" t="n">
-        <v>46320.47291666667</v>
+        <v>46312.47291666667</v>
       </c>
       <c r="E70" s="53" t="n">
-        <v>46320.49027777778</v>
+        <v>46312.49027777778</v>
       </c>
       <c r="F70" s="21">
         <f>IF(OR(D70="",E70=""),"",ROUND((E70-D70)*1440,0))</f>
@@ -20762,13 +20762,13 @@
         </is>
       </c>
       <c r="C71" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D71" s="53" t="n">
-        <v>46320.56041666667</v>
+        <v>46312.56041666667</v>
       </c>
       <c r="E71" s="53" t="n">
-        <v>46320.57777777778</v>
+        <v>46312.57777777778</v>
       </c>
       <c r="F71" s="21">
         <f>IF(OR(D71="",E71=""),"",ROUND((E71-D71)*1440,0))</f>
@@ -20804,13 +20804,13 @@
         </is>
       </c>
       <c r="C72" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D72" s="53" t="n">
-        <v>46320.60416666666</v>
+        <v>46312.60416666666</v>
       </c>
       <c r="E72" s="53" t="n">
-        <v>46320.62152777778</v>
+        <v>46312.62152777778</v>
       </c>
       <c r="F72" s="21">
         <f>IF(OR(D72="",E72=""),"",ROUND((E72-D72)*1440,0))</f>
@@ -20846,13 +20846,13 @@
         </is>
       </c>
       <c r="C73" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D73" s="53" t="n">
-        <v>46320.64791666667</v>
+        <v>46312.64791666667</v>
       </c>
       <c r="E73" s="53" t="n">
-        <v>46320.66527777778</v>
+        <v>46312.66527777778</v>
       </c>
       <c r="F73" s="21">
         <f>IF(OR(D73="",E73=""),"",ROUND((E73-D73)*1440,0))</f>
@@ -20888,13 +20888,13 @@
         </is>
       </c>
       <c r="C74" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D74" s="53" t="n">
-        <v>46320.44166666667</v>
+        <v>46312.44166666667</v>
       </c>
       <c r="E74" s="53" t="n">
-        <v>46320.45902777778</v>
+        <v>46312.45902777778</v>
       </c>
       <c r="F74" s="21">
         <f>IF(OR(D74="",E74=""),"",ROUND((E74-D74)*1440,0))</f>
@@ -20930,13 +20930,13 @@
         </is>
       </c>
       <c r="C75" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D75" s="53" t="n">
-        <v>46320.48541666667</v>
+        <v>46312.48541666667</v>
       </c>
       <c r="E75" s="53" t="n">
-        <v>46320.50277777778</v>
+        <v>46312.50277777778</v>
       </c>
       <c r="F75" s="21">
         <f>IF(OR(D75="",E75=""),"",ROUND((E75-D75)*1440,0))</f>
@@ -20972,13 +20972,13 @@
         </is>
       </c>
       <c r="C76" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D76" s="53" t="n">
-        <v>46320.52916666667</v>
+        <v>46312.52916666667</v>
       </c>
       <c r="E76" s="53" t="n">
-        <v>46320.54652777778</v>
+        <v>46312.54652777778</v>
       </c>
       <c r="F76" s="21">
         <f>IF(OR(D76="",E76=""),"",ROUND((E76-D76)*1440,0))</f>
@@ -21014,13 +21014,13 @@
         </is>
       </c>
       <c r="C77" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D77" s="53" t="n">
-        <v>46320.57291666666</v>
+        <v>46312.57291666666</v>
       </c>
       <c r="E77" s="53" t="n">
-        <v>46320.59027777778</v>
+        <v>46312.59027777778</v>
       </c>
       <c r="F77" s="21">
         <f>IF(OR(D77="",E77=""),"",ROUND((E77-D77)*1440,0))</f>
@@ -21056,13 +21056,13 @@
         </is>
       </c>
       <c r="C78" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D78" s="53" t="n">
-        <v>46320.61666666667</v>
+        <v>46312.61666666667</v>
       </c>
       <c r="E78" s="53" t="n">
-        <v>46320.63402777778</v>
+        <v>46312.63402777778</v>
       </c>
       <c r="F78" s="21">
         <f>IF(OR(D78="",E78=""),"",ROUND((E78-D78)*1440,0))</f>
@@ -21098,13 +21098,13 @@
         </is>
       </c>
       <c r="C79" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D79" s="53" t="n">
-        <v>46320.66041666667</v>
+        <v>46312.66041666667</v>
       </c>
       <c r="E79" s="53" t="n">
-        <v>46320.67777777778</v>
+        <v>46312.67777777778</v>
       </c>
       <c r="F79" s="21">
         <f>IF(OR(D79="",E79=""),"",ROUND((E79-D79)*1440,0))</f>
@@ -21140,13 +21140,13 @@
         </is>
       </c>
       <c r="C80" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D80" s="53" t="n">
-        <v>46320.45416666667</v>
+        <v>46312.45416666667</v>
       </c>
       <c r="E80" s="53" t="n">
-        <v>46320.47152777778</v>
+        <v>46312.47152777778</v>
       </c>
       <c r="F80" s="21">
         <f>IF(OR(D80="",E80=""),"",ROUND((E80-D80)*1440,0))</f>
@@ -21182,13 +21182,13 @@
         </is>
       </c>
       <c r="C81" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D81" s="53" t="n">
-        <v>46320.49791666667</v>
+        <v>46312.49791666667</v>
       </c>
       <c r="E81" s="53" t="n">
-        <v>46320.51527777778</v>
+        <v>46312.51527777778</v>
       </c>
       <c r="F81" s="21">
         <f>IF(OR(D81="",E81=""),"",ROUND((E81-D81)*1440,0))</f>
@@ -21224,13 +21224,13 @@
         </is>
       </c>
       <c r="C82" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D82" s="53" t="n">
-        <v>46320.5</v>
+        <v>46312.5</v>
       </c>
       <c r="E82" s="53" t="n">
-        <v>46320.51736111111</v>
+        <v>46312.51736111111</v>
       </c>
       <c r="F82" s="21">
         <f>IF(OR(D82="",E82=""),"",ROUND((E82-D82)*1440,0))</f>
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="C83" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D83" s="53" t="n">
-        <v>46320.54375</v>
+        <v>46312.54375</v>
       </c>
       <c r="E83" s="53" t="n">
-        <v>46320.56111111111</v>
+        <v>46312.56111111111</v>
       </c>
       <c r="F83" s="21">
         <f>IF(OR(D83="",E83=""),"",ROUND((E83-D83)*1440,0))</f>
@@ -21308,13 +21308,13 @@
         </is>
       </c>
       <c r="C84" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D84" s="53" t="n">
-        <v>46320.5875</v>
+        <v>46312.5875</v>
       </c>
       <c r="E84" s="53" t="n">
-        <v>46320.60486111111</v>
+        <v>46312.60486111111</v>
       </c>
       <c r="F84" s="21">
         <f>IF(OR(D84="",E84=""),"",ROUND((E84-D84)*1440,0))</f>
@@ -21350,13 +21350,13 @@
         </is>
       </c>
       <c r="C85" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D85" s="53" t="n">
-        <v>46320.63125</v>
+        <v>46312.63125</v>
       </c>
       <c r="E85" s="53" t="n">
-        <v>46320.64861111111</v>
+        <v>46312.64861111111</v>
       </c>
       <c r="F85" s="21">
         <f>IF(OR(D85="",E85=""),"",ROUND((E85-D85)*1440,0))</f>
@@ -21392,13 +21392,13 @@
         </is>
       </c>
       <c r="C86" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D86" s="53" t="n">
-        <v>46320.425</v>
+        <v>46312.425</v>
       </c>
       <c r="E86" s="53" t="n">
-        <v>46320.44236111111</v>
+        <v>46312.44236111111</v>
       </c>
       <c r="F86" s="21">
         <f>IF(OR(D86="",E86=""),"",ROUND((E86-D86)*1440,0))</f>
@@ -21434,13 +21434,13 @@
         </is>
       </c>
       <c r="C87" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D87" s="53" t="n">
-        <v>46320.46875</v>
+        <v>46312.46875</v>
       </c>
       <c r="E87" s="53" t="n">
-        <v>46320.48611111111</v>
+        <v>46312.48611111111</v>
       </c>
       <c r="F87" s="21">
         <f>IF(OR(D87="",E87=""),"",ROUND((E87-D87)*1440,0))</f>
@@ -21476,13 +21476,13 @@
         </is>
       </c>
       <c r="C88" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D88" s="53" t="n">
-        <v>46320.5125</v>
+        <v>46312.5125</v>
       </c>
       <c r="E88" s="53" t="n">
-        <v>46320.52986111111</v>
+        <v>46312.52986111111</v>
       </c>
       <c r="F88" s="21">
         <f>IF(OR(D88="",E88=""),"",ROUND((E88-D88)*1440,0))</f>
@@ -21518,13 +21518,13 @@
         </is>
       </c>
       <c r="C89" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D89" s="53" t="n">
-        <v>46320.55625</v>
+        <v>46312.55625</v>
       </c>
       <c r="E89" s="53" t="n">
-        <v>46320.57361111111</v>
+        <v>46312.57361111111</v>
       </c>
       <c r="F89" s="21">
         <f>IF(OR(D89="",E89=""),"",ROUND((E89-D89)*1440,0))</f>
@@ -21560,13 +21560,13 @@
         </is>
       </c>
       <c r="C90" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D90" s="53" t="n">
-        <v>46320.6</v>
+        <v>46312.6</v>
       </c>
       <c r="E90" s="53" t="n">
-        <v>46320.61736111111</v>
+        <v>46312.61736111111</v>
       </c>
       <c r="F90" s="21">
         <f>IF(OR(D90="",E90=""),"",ROUND((E90-D90)*1440,0))</f>
@@ -21602,13 +21602,13 @@
         </is>
       </c>
       <c r="C91" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D91" s="53" t="n">
-        <v>46320.64375</v>
+        <v>46312.64375</v>
       </c>
       <c r="E91" s="53" t="n">
-        <v>46320.66111111111</v>
+        <v>46312.66111111111</v>
       </c>
       <c r="F91" s="21">
         <f>IF(OR(D91="",E91=""),"",ROUND((E91-D91)*1440,0))</f>
@@ -21644,13 +21644,13 @@
         </is>
       </c>
       <c r="C92" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D92" s="53" t="n">
-        <v>46320.4375</v>
+        <v>46312.4375</v>
       </c>
       <c r="E92" s="53" t="n">
-        <v>46320.45486111111</v>
+        <v>46312.45486111111</v>
       </c>
       <c r="F92" s="21">
         <f>IF(OR(D92="",E92=""),"",ROUND((E92-D92)*1440,0))</f>
@@ -21686,13 +21686,13 @@
         </is>
       </c>
       <c r="C93" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D93" s="53" t="n">
-        <v>46320.48125</v>
+        <v>46312.48125</v>
       </c>
       <c r="E93" s="53" t="n">
-        <v>46320.49861111111</v>
+        <v>46312.49861111111</v>
       </c>
       <c r="F93" s="21">
         <f>IF(OR(D93="",E93=""),"",ROUND((E93-D93)*1440,0))</f>
@@ -21728,13 +21728,13 @@
         </is>
       </c>
       <c r="C94" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D94" s="53" t="n">
-        <v>46320.525</v>
+        <v>46312.525</v>
       </c>
       <c r="E94" s="53" t="n">
-        <v>46320.54236111111</v>
+        <v>46312.54236111111</v>
       </c>
       <c r="F94" s="21">
         <f>IF(OR(D94="",E94=""),"",ROUND((E94-D94)*1440,0))</f>
@@ -21770,13 +21770,13 @@
         </is>
       </c>
       <c r="C95" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D95" s="53" t="n">
-        <v>46320.56875</v>
+        <v>46312.56875</v>
       </c>
       <c r="E95" s="53" t="n">
-        <v>46320.58611111111</v>
+        <v>46312.58611111111</v>
       </c>
       <c r="F95" s="21">
         <f>IF(OR(D95="",E95=""),"",ROUND((E95-D95)*1440,0))</f>
@@ -21812,13 +21812,13 @@
         </is>
       </c>
       <c r="C96" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D96" s="53" t="n">
-        <v>46320.65625</v>
+        <v>46312.65625</v>
       </c>
       <c r="E96" s="53" t="n">
-        <v>46320.67361111111</v>
+        <v>46312.67361111111</v>
       </c>
       <c r="F96" s="21">
         <f>IF(OR(D96="",E96=""),"",ROUND((E96-D96)*1440,0))</f>
@@ -21854,13 +21854,13 @@
         </is>
       </c>
       <c r="C97" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D97" s="53" t="n">
-        <v>46320.49375</v>
+        <v>46312.49375</v>
       </c>
       <c r="E97" s="53" t="n">
-        <v>46320.51111111111</v>
+        <v>46312.51111111111</v>
       </c>
       <c r="F97" s="21">
         <f>IF(OR(D97="",E97=""),"",ROUND((E97-D97)*1440,0))</f>
@@ -21896,13 +21896,13 @@
         </is>
       </c>
       <c r="C98" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D98" s="53" t="n">
-        <v>46320.5375</v>
+        <v>46312.5375</v>
       </c>
       <c r="E98" s="53" t="n">
-        <v>46320.55486111111</v>
+        <v>46312.55486111111</v>
       </c>
       <c r="F98" s="21">
         <f>IF(OR(D98="",E98=""),"",ROUND((E98-D98)*1440,0))</f>
@@ -21938,13 +21938,13 @@
         </is>
       </c>
       <c r="C99" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D99" s="53" t="n">
-        <v>46320.58125</v>
+        <v>46312.58125</v>
       </c>
       <c r="E99" s="53" t="n">
-        <v>46320.59861111111</v>
+        <v>46312.59861111111</v>
       </c>
       <c r="F99" s="21">
         <f>IF(OR(D99="",E99=""),"",ROUND((E99-D99)*1440,0))</f>
@@ -21980,13 +21980,13 @@
         </is>
       </c>
       <c r="C100" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D100" s="53" t="n">
-        <v>46320.58333333334</v>
+        <v>46312.58333333334</v>
       </c>
       <c r="E100" s="53" t="n">
-        <v>46320.60069444445</v>
+        <v>46312.60069444445</v>
       </c>
       <c r="F100" s="21">
         <f>IF(OR(D100="",E100=""),"",ROUND((E100-D100)*1440,0))</f>
@@ -22022,13 +22022,13 @@
         </is>
       </c>
       <c r="C101" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D101" s="53" t="n">
-        <v>46320.62708333333</v>
+        <v>46312.62708333333</v>
       </c>
       <c r="E101" s="53" t="n">
-        <v>46320.64444444444</v>
+        <v>46312.64444444444</v>
       </c>
       <c r="F101" s="21">
         <f>IF(OR(D101="",E101=""),"",ROUND((E101-D101)*1440,0))</f>
@@ -22064,13 +22064,13 @@
         </is>
       </c>
       <c r="C102" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D102" s="53" t="n">
-        <v>46320.42083333333</v>
+        <v>46312.42083333333</v>
       </c>
       <c r="E102" s="53" t="n">
-        <v>46320.43819444445</v>
+        <v>46312.43819444445</v>
       </c>
       <c r="F102" s="21">
         <f>IF(OR(D102="",E102=""),"",ROUND((E102-D102)*1440,0))</f>
@@ -22106,13 +22106,13 @@
         </is>
       </c>
       <c r="C103" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D103" s="53" t="n">
-        <v>46320.46458333333</v>
+        <v>46312.46458333333</v>
       </c>
       <c r="E103" s="53" t="n">
-        <v>46320.48194444444</v>
+        <v>46312.48194444444</v>
       </c>
       <c r="F103" s="21">
         <f>IF(OR(D103="",E103=""),"",ROUND((E103-D103)*1440,0))</f>
@@ -22148,13 +22148,13 @@
         </is>
       </c>
       <c r="C104" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D104" s="53" t="n">
-        <v>46320.50833333333</v>
+        <v>46312.50833333333</v>
       </c>
       <c r="E104" s="53" t="n">
-        <v>46320.52569444444</v>
+        <v>46312.52569444444</v>
       </c>
       <c r="F104" s="21">
         <f>IF(OR(D104="",E104=""),"",ROUND((E104-D104)*1440,0))</f>
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="C105" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D105" s="53" t="n">
-        <v>46320.59583333333</v>
+        <v>46312.59583333333</v>
       </c>
       <c r="E105" s="53" t="n">
-        <v>46320.61319444444</v>
+        <v>46312.61319444444</v>
       </c>
       <c r="F105" s="21">
         <f>IF(OR(D105="",E105=""),"",ROUND((E105-D105)*1440,0))</f>
@@ -22232,13 +22232,13 @@
         </is>
       </c>
       <c r="C106" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D106" s="53" t="n">
-        <v>46320.43333333333</v>
+        <v>46312.43333333333</v>
       </c>
       <c r="E106" s="53" t="n">
-        <v>46320.45069444444</v>
+        <v>46312.45069444444</v>
       </c>
       <c r="F106" s="21">
         <f>IF(OR(D106="",E106=""),"",ROUND((E106-D106)*1440,0))</f>
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="C107" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D107" s="53" t="n">
-        <v>46320.47708333333</v>
+        <v>46312.47708333333</v>
       </c>
       <c r="E107" s="53" t="n">
-        <v>46320.49444444444</v>
+        <v>46312.49444444444</v>
       </c>
       <c r="F107" s="21">
         <f>IF(OR(D107="",E107=""),"",ROUND((E107-D107)*1440,0))</f>
@@ -22316,13 +22316,13 @@
         </is>
       </c>
       <c r="C108" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D108" s="53" t="n">
-        <v>46320.52083333334</v>
+        <v>46312.52083333334</v>
       </c>
       <c r="E108" s="53" t="n">
-        <v>46320.53819444445</v>
+        <v>46312.53819444445</v>
       </c>
       <c r="F108" s="21">
         <f>IF(OR(D108="",E108=""),"",ROUND((E108-D108)*1440,0))</f>
@@ -22358,13 +22358,13 @@
         </is>
       </c>
       <c r="C109" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D109" s="53" t="n">
-        <v>46320.56458333333</v>
+        <v>46312.56458333333</v>
       </c>
       <c r="E109" s="53" t="n">
-        <v>46320.58194444444</v>
+        <v>46312.58194444444</v>
       </c>
       <c r="F109" s="21">
         <f>IF(OR(D109="",E109=""),"",ROUND((E109-D109)*1440,0))</f>
@@ -22400,13 +22400,13 @@
         </is>
       </c>
       <c r="C110" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D110" s="53" t="n">
-        <v>46320.65208333333</v>
+        <v>46312.65208333333</v>
       </c>
       <c r="E110" s="53" t="n">
-        <v>46320.66944444444</v>
+        <v>46312.66944444444</v>
       </c>
       <c r="F110" s="21">
         <f>IF(OR(D110="",E110=""),"",ROUND((E110-D110)*1440,0))</f>
@@ -22442,13 +22442,13 @@
         </is>
       </c>
       <c r="C111" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D111" s="53" t="n">
-        <v>46320.44583333333</v>
+        <v>46312.44583333333</v>
       </c>
       <c r="E111" s="53" t="n">
-        <v>46320.46319444444</v>
+        <v>46312.46319444444</v>
       </c>
       <c r="F111" s="21">
         <f>IF(OR(D111="",E111=""),"",ROUND((E111-D111)*1440,0))</f>
@@ -22484,13 +22484,13 @@
         </is>
       </c>
       <c r="C112" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D112" s="53" t="n">
-        <v>46320.48958333334</v>
+        <v>46312.48958333334</v>
       </c>
       <c r="E112" s="53" t="n">
-        <v>46320.50694444445</v>
+        <v>46312.50694444445</v>
       </c>
       <c r="F112" s="21">
         <f>IF(OR(D112="",E112=""),"",ROUND((E112-D112)*1440,0))</f>
@@ -22526,13 +22526,13 @@
         </is>
       </c>
       <c r="C113" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D113" s="53" t="n">
-        <v>46320.53333333333</v>
+        <v>46312.53333333333</v>
       </c>
       <c r="E113" s="53" t="n">
-        <v>46320.55069444444</v>
+        <v>46312.55069444444</v>
       </c>
       <c r="F113" s="21">
         <f>IF(OR(D113="",E113=""),"",ROUND((E113-D113)*1440,0))</f>
@@ -22568,13 +22568,13 @@
         </is>
       </c>
       <c r="C114" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D114" s="53" t="n">
-        <v>46320.57708333333</v>
+        <v>46312.57708333333</v>
       </c>
       <c r="E114" s="53" t="n">
-        <v>46320.59444444445</v>
+        <v>46312.59444444445</v>
       </c>
       <c r="F114" s="21">
         <f>IF(OR(D114="",E114=""),"",ROUND((E114-D114)*1440,0))</f>
@@ -22610,13 +22610,13 @@
         </is>
       </c>
       <c r="C115" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D115" s="53" t="n">
-        <v>46320.62083333333</v>
+        <v>46312.62083333333</v>
       </c>
       <c r="E115" s="53" t="n">
-        <v>46320.63819444444</v>
+        <v>46312.63819444444</v>
       </c>
       <c r="F115" s="21">
         <f>IF(OR(D115="",E115=""),"",ROUND((E115-D115)*1440,0))</f>
@@ -22652,13 +22652,13 @@
         </is>
       </c>
       <c r="C116" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D116" s="53" t="n">
-        <v>46320.66458333333</v>
+        <v>46312.66458333333</v>
       </c>
       <c r="E116" s="53" t="n">
-        <v>46320.68194444444</v>
+        <v>46312.68194444444</v>
       </c>
       <c r="F116" s="21">
         <f>IF(OR(D116="",E116=""),"",ROUND((E116-D116)*1440,0))</f>
@@ -22694,13 +22694,13 @@
         </is>
       </c>
       <c r="C117" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D117" s="53" t="n">
-        <v>46320.41666666666</v>
+        <v>46312.41666666666</v>
       </c>
       <c r="E117" s="53" t="n">
-        <v>46320.43402777778</v>
+        <v>46312.43402777778</v>
       </c>
       <c r="F117" s="21">
         <f>IF(OR(D117="",E117=""),"",ROUND((E117-D117)*1440,0))</f>
@@ -22736,13 +22736,13 @@
         </is>
       </c>
       <c r="C118" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D118" s="53" t="n">
-        <v>46320.46041666667</v>
+        <v>46312.46041666667</v>
       </c>
       <c r="E118" s="53" t="n">
-        <v>46320.47777777778</v>
+        <v>46312.47777777778</v>
       </c>
       <c r="F118" s="21">
         <f>IF(OR(D118="",E118=""),"",ROUND((E118-D118)*1440,0))</f>
@@ -22778,13 +22778,13 @@
         </is>
       </c>
       <c r="C119" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D119" s="53" t="n">
-        <v>46320.50416666667</v>
+        <v>46312.50416666667</v>
       </c>
       <c r="E119" s="53" t="n">
-        <v>46320.52152777778</v>
+        <v>46312.52152777778</v>
       </c>
       <c r="F119" s="21">
         <f>IF(OR(D119="",E119=""),"",ROUND((E119-D119)*1440,0))</f>
@@ -22820,13 +22820,13 @@
         </is>
       </c>
       <c r="C120" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D120" s="53" t="n">
-        <v>46320.59166666667</v>
+        <v>46312.59166666667</v>
       </c>
       <c r="E120" s="53" t="n">
-        <v>46320.60902777778</v>
+        <v>46312.60902777778</v>
       </c>
       <c r="F120" s="21">
         <f>IF(OR(D120="",E120=""),"",ROUND((E120-D120)*1440,0))</f>
@@ -22862,13 +22862,13 @@
         </is>
       </c>
       <c r="C121" s="52" t="n">
-        <v>46320</v>
+        <v>46312</v>
       </c>
       <c r="D121" s="53" t="n">
-        <v>46320.63541666666</v>
+        <v>46312.63541666666</v>
       </c>
       <c r="E121" s="53" t="n">
-        <v>46320.65277777778</v>
+        <v>46312.65277777778</v>
       </c>
       <c r="F121" s="21">
         <f>IF(OR(D121="",E121=""),"",ROUND((E121-D121)*1440,0))</f>
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="B12" s="49" t="n">
-        <v>46321.79861111111</v>
+        <v>46313.79861111111</v>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         </is>
       </c>
       <c r="H12" s="49" t="n">
-        <v>46321.81944444445</v>
+        <v>46313.81944444445</v>
       </c>
       <c r="I12" s="24">
         <f>IF(OR(B12="",H12=""),"",ROUND((H12-B12)*24,1))</f>
@@ -24106,7 +24106,7 @@
         </is>
       </c>
       <c r="B13" s="49" t="n">
-        <v>46322.42708333334</v>
+        <v>46314.42708333334</v>
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         </is>
       </c>
       <c r="H13" s="49" t="n">
-        <v>46322.43611111111</v>
+        <v>46314.43611111111</v>
       </c>
       <c r="I13" s="21">
         <f>IF(OR(B13="",H13=""),"",ROUND((H13-B13)*24,1))</f>
@@ -24158,7 +24158,7 @@
         </is>
       </c>
       <c r="B14" s="49" t="n">
-        <v>46322.43055555555</v>
+        <v>46314.43055555555</v>
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="H14" s="49" t="n">
-        <v>46322.44097222222</v>
+        <v>46314.44097222222</v>
       </c>
       <c r="I14" s="21">
         <f>IF(OR(B14="",H14=""),"",ROUND((H14-B14)*24,1))</f>
@@ -24210,7 +24210,7 @@
         </is>
       </c>
       <c r="B15" s="49" t="n">
-        <v>46323.67013888889</v>
+        <v>46315.67013888889</v>
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         </is>
       </c>
       <c r="H15" s="49" t="n">
-        <v>46323.72222222222</v>
+        <v>46315.72222222222</v>
       </c>
       <c r="I15" s="21">
         <f>IF(OR(B15="",H15=""),"",ROUND((H15-B15)*24,1))</f>
@@ -24262,7 +24262,7 @@
         </is>
       </c>
       <c r="B16" s="49" t="n">
-        <v>46324.5</v>
+        <v>46316.5</v>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         </is>
       </c>
       <c r="H16" s="49" t="n">
-        <v>46324.51736111111</v>
+        <v>46316.51736111111</v>
       </c>
       <c r="I16" s="21">
         <f>IF(OR(B16="",H16=""),"",ROUND((H16-B16)*24,1))</f>
@@ -24314,7 +24314,7 @@
         </is>
       </c>
       <c r="B17" s="49" t="n">
-        <v>46325.45972222222</v>
+        <v>46317.45972222222</v>
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         </is>
       </c>
       <c r="H17" s="49" t="n">
-        <v>46325.46527777778</v>
+        <v>46317.46527777778</v>
       </c>
       <c r="I17" s="21">
         <f>IF(OR(B17="",H17=""),"",ROUND((H17-B17)*24,1))</f>
@@ -24366,7 +24366,7 @@
         </is>
       </c>
       <c r="B18" s="49" t="n">
-        <v>46327.40972222222</v>
+        <v>46319.40972222222</v>
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         </is>
       </c>
       <c r="H18" s="49" t="n">
-        <v>46327.42361111111</v>
+        <v>46319.42361111111</v>
       </c>
       <c r="I18" s="21">
         <f>IF(OR(B18="",H18=""),"",ROUND((H18-B18)*24,1))</f>
@@ -26099,7 +26099,7 @@
         </is>
       </c>
       <c r="B11" s="54" t="n">
-        <v>46322.375</v>
+        <v>46314.375</v>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         </is>
       </c>
       <c r="B12" s="54" t="n">
-        <v>46328.99930555555</v>
+        <v>46320.99930555555</v>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         </is>
       </c>
       <c r="D16" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="71">
@@ -26199,7 +26199,7 @@
         </is>
       </c>
       <c r="D17" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="71">
@@ -26219,7 +26219,7 @@
         </is>
       </c>
       <c r="D18" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="71">
@@ -26239,7 +26239,7 @@
         </is>
       </c>
       <c r="D19" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="71">
@@ -26259,7 +26259,7 @@
         </is>
       </c>
       <c r="D20" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="71">
@@ -26279,7 +26279,7 @@
         </is>
       </c>
       <c r="D21" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="71">
@@ -26299,7 +26299,7 @@
         </is>
       </c>
       <c r="D22" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="71">
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="D23" s="76" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="71"/>
